--- a/光伏配储项目/电价数据/2026/官埭站.xlsx
+++ b/光伏配储项目/电价数据/2026/官埭站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.29403</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07532</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.74026</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.62348</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17307</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26921</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25434</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25894</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.62928</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44773</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.71484</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6682100000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.8764500000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.69589</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.49452</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.79072</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.02945</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.71296</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.09383</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.48686</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.05711</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.05597</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.41978</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.43596</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45787</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.81667</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8793200000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.07942</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6842999999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.46622</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.83873</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.59234</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.20707</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.30841</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6632100000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.37344</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.10851</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.09242</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.10133</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.10193</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.10997</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.21069</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.12702</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.23931</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.21653</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.57009</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.70533</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.67004</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.66728</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.62842</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.12799</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.84113</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.96868</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.60977</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5534</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.8815299999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.25135</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.8227300000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8509099999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.08978</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.49339</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.06243</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.12126</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.07788</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.23359</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03743</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.06261</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9707899999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.13972</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.96338</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8578300000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.0326</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.07189</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.54937</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.00633</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80228</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.5416299999999999</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.50482</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.5330499999999999</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.31539</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.22054</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.18552</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.22069</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.20497</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.25432</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.17949</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.15581</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.24847</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.20695</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.24179</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.25306</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.24655</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.23629</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.23141</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.19705</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.27796</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.13854</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.90113</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.89066</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.03926</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.03852</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1.0758</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.04439</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.05565999999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.78274</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.79565</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.81424</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.3832</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.7320399999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.8711599999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.13185</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.08316</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.9300900000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8745299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.6660900000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.99836</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.69077</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45793</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51386</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50312</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.50974</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.54526</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.63822</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6180099999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.50087</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.8293400000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70299</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48841</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.48987</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6995</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.98029</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.83396</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.9464600000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.49938</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.64486</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.5237200000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.59305</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.67698</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.84376</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.60085</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.08082</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.7269099999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.6195499999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7980700000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.5050899999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.54271</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.32137</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.21975</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.21937</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.23735</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.26659</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.26779</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.25978</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.26373</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.21355</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.26659</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.26531</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.27616</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.44276</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.46433</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.48705</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.6116</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7932100000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47972</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46496</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7683</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.59008</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.54325</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.61913</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.83792</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.66934</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.50949</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.47089</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.53938</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.7315900000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.72661</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.75754</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.5647799999999999</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.6057400000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.70885</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8456699999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.63959</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66483</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6797799999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.65304</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.55753</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.5223099999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.51008</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.49473</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.5691000000000001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14338</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02446</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.46507</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26662</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10602</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03175</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26345</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31722</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.58982</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24088</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24722</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.53179</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.52786</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24878</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.51102</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21489</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19272</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.51158</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17416</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20124</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.07359</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20616</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04924</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19419</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05851</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31577</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.49237</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.50125</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5796</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.66384</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.79727</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87033</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6544</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57243</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.52039</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.7732100000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.77207</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.26606</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.57656</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.46117</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.78624</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.01903</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26598</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43267</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.79927</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64523</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32359</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.81152</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.28516</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.5952000000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.55822</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.62295</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.63614</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45699</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.52385</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.5935900000000001</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.66547</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.63787</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.58696</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.63567</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.6414299999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.74148</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.58202</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.5437799999999999</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.62452</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.59576</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.48126</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.5757899999999999</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.88919</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.67237</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.61776</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.68604</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.6710199999999999</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.6319199999999999</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.53506</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.62498</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.6288899999999999</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.6196699999999999</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.5783200000000001</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.60753</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.6192300000000001</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.6120800000000001</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.58285</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.6252000000000001</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.63493</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.65386</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.64655</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.62464</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.55443</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.85588</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.66988</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.83257</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.48937</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.47871</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5002</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.5009</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.8938200000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.79952</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.25497</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.20791</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.10336</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="V126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.25934</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.46331</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.6498700000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.46645</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.59523</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.51434</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.44604</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.45831</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.20523</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.66083</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.46097</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.45897</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.5727000000000001</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.51707</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.52246</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.57362</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.56736</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.57663</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.54747</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.56588</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.54314</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.5316799999999999</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.5544</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.55353</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.48918</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.09639</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.47929</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18652</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18375</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.25648</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.46621</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.46599</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.48946</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18642</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.43063</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.57697</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.42452</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.45245</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24874</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43448</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30405</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.02315</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.63866</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48049</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49058</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48746</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54013</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.01815</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.9109700000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.70311</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52924</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.5388999999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.7607999999999999</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.73736</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.9581499999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.30518</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.43265</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.8844299999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.7977799999999999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.74224</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.65104</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.53479</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.7819700000000001</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.61078</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.5866399999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.5327799999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20042</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19259</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19175</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15584</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23626</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19149</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.49621</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20406</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16033</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.53908</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.5491699999999999</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.6309900000000001</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.52377</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.6084700000000001</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26682</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.50998</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23577</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32335</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27468</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5764900000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20707</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29727</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44411</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49957</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.60517</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5692</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6152000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7546</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47409</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3148</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44009</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47051</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.50963</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5779099999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64454</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.68599</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48203</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.72089</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.49751</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.66818</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.54738</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31785</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26853</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.00196</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.67187</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.70074</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.8603200000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.49102</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.54364</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.59115</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.7392000000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.80926</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.5619400000000001</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.60441</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.5486799999999999</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.56659</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.65058</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.51129</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.49217</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.54395</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.25725</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16879</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.00256</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.00211</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16902</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.01343</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20159</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16782</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.00294</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15833</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16052</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16325</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16599</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.00364</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16872</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.00378</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.02864</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17969</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15076</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.02435</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.5166499999999999</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.48728</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.45964</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.5395800000000001</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.70463</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.46227</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.20312</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0008900000000000001</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.49645</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.53199</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.44859</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.42669</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.44246</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.49447</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.56369</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.48216</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.43809</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.49226</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.46931</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.49247</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22087</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.52315</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24693</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.5976900000000001</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.54096</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22969</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.04388</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18586</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18288</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.01268</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20243</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22326</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.03221</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.02417</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.01043</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01044</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01062</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19709</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.02451</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01084</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17628</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.02417</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.02416</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01119</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24461</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.02862</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00715</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.01961</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.06927</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.00378</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.18863</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.01739</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.009810000000000001</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2696</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17043</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16529</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16967</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.16704</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.03452</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15197</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.03395</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.03547</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.03387</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.00435</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.00261</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.19425</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.0352</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23673</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85784</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86207</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09124</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01049</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.50359</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06905</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47517</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.64485</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50476</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7422000000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.85636</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57263</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.68678</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.73112</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7293500000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.73273</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.81331</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.42295</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30809</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.1921</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25951</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25444</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21586</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20291</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19849</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16258</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16527</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.03507</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15913</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18292</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24193</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25858</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29189</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5463899999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.22857</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7373200000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.75734</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.51108</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6474299999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.77543</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41163</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.44573</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20115</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31688</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.67137</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.66653</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.48726</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.6162799999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.65152</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55444</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32148</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.03614</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.55837</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43502</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.52866</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.51461</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5889800000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32551</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6605599999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4362</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45894</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.46691</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42277</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42959</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33842</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14576</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19865</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14637</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12168</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22614</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14541</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22684</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.49208</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.22069</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.53877</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40913</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42021</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.47755</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.53432</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.64666</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.46352</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43562</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4869</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40667</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36825</v>
       </c>
     </row>
   </sheetData>
